--- a/testdata/configurationUAT/listForExecution.xlsx
+++ b/testdata/configurationUAT/listForExecution.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="22728" windowHeight="9528"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,8 @@
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$B$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="363">
   <si>
     <t>TestName</t>
   </si>
@@ -289,6 +290,9 @@
     <t>C70802</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
   </si>
   <si>
@@ -889,7 +893,7 @@
     <t>C70902</t>
   </si>
   <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Current_Domestic_Account</t>
   </si>
   <si>
     <t>C70903</t>
@@ -958,6 +962,144 @@
     <t>C70914</t>
   </si>
   <si>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70915</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Card_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70917</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70918</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Internal_Transfer</t>
+  </si>
+  <si>
+    <t>C70919</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Domestic_Payment</t>
+  </si>
+  <si>
+    <t>C70920</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Prenesi</t>
+  </si>
+  <si>
+    <t>C70921</t>
+  </si>
+  <si>
+    <t>C70922</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70923</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
+    <t>General_Dashboard_Page_overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70926</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70927</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70928</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70929</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_Downloads_[WEB]</t>
+  </si>
+  <si>
+    <t>C70930</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Downloads_[WEB]</t>
+  </si>
+  <si>
+    <t>C70931</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -973,7 +1115,8 @@
     <t>Automated Test Names</t>
   </si>
   <si>
-    <t>Credit_Cards_Details_Card_Details_[WEB]</t>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account
+Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Accoun</t>
   </si>
   <si>
     <r>
@@ -983,7 +1126,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account</t>
+      <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Current_Domestic_Account</t>
     </r>
     <r>
       <rPr>
@@ -1002,7 +1145,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Accoun</t>
+      <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Savings_Account</t>
     </r>
   </si>
   <si>
@@ -1763,7 +1906,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1778,6 +1921,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2109,7 +2258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -2149,7 +2298,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A2)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A2,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -2170,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A3)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A3,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -2191,7 +2340,7 @@
         <v>9</v>
       </c>
       <c r="E4" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A4)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A4,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -2212,7 +2361,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A5)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A5,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -2233,7 +2382,7 @@
         <v>9</v>
       </c>
       <c r="E6" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A6)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A6,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -2254,8 +2403,8 @@
         <v>9</v>
       </c>
       <c r="E7" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A7)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A7,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>10</v>
@@ -2275,8 +2424,8 @@
         <v>9</v>
       </c>
       <c r="E8" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A8)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A8,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>10</v>
@@ -2296,7 +2445,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A9)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A9,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F9" t="s">
@@ -2317,7 +2466,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A10)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A10,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F10" t="s">
@@ -2338,7 +2487,7 @@
         <v>9</v>
       </c>
       <c r="E11" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A11)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A11,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F11" t="s">
@@ -2359,8 +2508,8 @@
         <v>9</v>
       </c>
       <c r="E12" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A12)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A12,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>10</v>
@@ -2380,7 +2529,7 @@
         <v>9</v>
       </c>
       <c r="E13" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A13)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A13,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -2401,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A14)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A14,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -2422,7 +2571,7 @@
         <v>9</v>
       </c>
       <c r="E15" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A15)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A15,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -2443,7 +2592,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A16)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A16,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -2464,7 +2613,7 @@
         <v>9</v>
       </c>
       <c r="E17" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A17)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A17,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -2485,7 +2634,7 @@
         <v>9</v>
       </c>
       <c r="E18" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A18)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A18,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F18" t="s">
@@ -2506,8 +2655,8 @@
         <v>9</v>
       </c>
       <c r="E19" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A19)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A19,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -2527,7 +2676,7 @@
         <v>9</v>
       </c>
       <c r="E20" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A20)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A20,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F20" t="s">
@@ -2548,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="E21" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A21)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A21,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F21" t="s">
@@ -2569,8 +2718,8 @@
         <v>9</v>
       </c>
       <c r="E22" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A22)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A22,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>10</v>
@@ -2590,8 +2739,8 @@
         <v>9</v>
       </c>
       <c r="E23" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A23)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A23,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>10</v>
@@ -2611,8 +2760,8 @@
         <v>9</v>
       </c>
       <c r="E24" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A24)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A24,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>10</v>
@@ -2632,7 +2781,7 @@
         <v>9</v>
       </c>
       <c r="E25" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A25)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A25,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F25" s="4" t="s">
@@ -2653,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="E26" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A26)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A26,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F26" s="4" t="s">
@@ -2674,7 +2823,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A27)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A27,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -2695,8 +2844,8 @@
         <v>9</v>
       </c>
       <c r="E28" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A28)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A28,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>10</v>
@@ -2716,7 +2865,7 @@
         <v>9</v>
       </c>
       <c r="E29" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A29)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A29,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F29" s="4" t="s">
@@ -2737,7 +2886,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A30)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A30,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F30" s="4" t="s">
@@ -2758,7 +2907,7 @@
         <v>9</v>
       </c>
       <c r="E31" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A31)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A31,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -2779,7 +2928,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A32)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A32,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -2800,7 +2949,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A33)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A33,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F33" s="4" t="s">
@@ -2821,7 +2970,7 @@
         <v>9</v>
       </c>
       <c r="E34" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A34)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A34,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F34" s="4" t="s">
@@ -2842,8 +2991,8 @@
         <v>9</v>
       </c>
       <c r="E35" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A35)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A35,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>10</v>
@@ -2863,8 +3012,8 @@
         <v>9</v>
       </c>
       <c r="E36" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A36)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A36,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>10</v>
@@ -2884,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="E37" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A37)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A37,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F37" s="4" t="s">
@@ -2905,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="E38" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A38)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A38,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F38" s="4" t="s">
@@ -2925,9 +3074,8 @@
       <c r="D39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E39" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A39)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E39" t="s">
+        <v>85</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>10</v>
@@ -2935,10 +3083,10 @@
     </row>
     <row r="40" customFormat="1" spans="1:6">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>8</v>
@@ -2947,7 +3095,7 @@
         <v>9</v>
       </c>
       <c r="E40" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A40)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A40,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F40" s="4" t="s">
@@ -2956,10 +3104,10 @@
     </row>
     <row r="41" customFormat="1" spans="1:6">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>8</v>
@@ -2968,8 +3116,8 @@
         <v>9</v>
       </c>
       <c r="E41" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A41)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A41,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>10</v>
@@ -2977,10 +3125,10 @@
     </row>
     <row r="42" customFormat="1" spans="1:6">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>8</v>
@@ -2989,7 +3137,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A42)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A42,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F42" t="s">
@@ -2998,10 +3146,10 @@
     </row>
     <row r="43" customFormat="1" spans="1:6">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>8</v>
@@ -3010,7 +3158,7 @@
         <v>9</v>
       </c>
       <c r="E43" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A43)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A43,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F43" t="s">
@@ -3019,10 +3167,10 @@
     </row>
     <row r="44" customFormat="1" spans="1:6">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
@@ -3031,7 +3179,7 @@
         <v>9</v>
       </c>
       <c r="E44" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A44)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A44,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F44" t="s">
@@ -3040,10 +3188,10 @@
     </row>
     <row r="45" customFormat="1" spans="1:6">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>8</v>
@@ -3052,8 +3200,8 @@
         <v>9</v>
       </c>
       <c r="E45" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A45)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A45,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>10</v>
@@ -3061,10 +3209,10 @@
     </row>
     <row r="46" customFormat="1" spans="1:6">
       <c r="A46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
@@ -3073,8 +3221,8 @@
         <v>9</v>
       </c>
       <c r="E46" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A46)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A46,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>10</v>
@@ -3082,10 +3230,10 @@
     </row>
     <row r="47" customFormat="1" spans="1:6">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
@@ -3094,7 +3242,7 @@
         <v>9</v>
       </c>
       <c r="E47" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A47)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A47,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F47" s="4" t="s">
@@ -3103,10 +3251,10 @@
     </row>
     <row r="48" customFormat="1" spans="1:6">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>8</v>
@@ -3115,8 +3263,8 @@
         <v>9</v>
       </c>
       <c r="E48" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A48)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A48,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>10</v>
@@ -3124,10 +3272,10 @@
     </row>
     <row r="49" customFormat="1" spans="1:6">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
@@ -3136,8 +3284,8 @@
         <v>9</v>
       </c>
       <c r="E49" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A49)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A49,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>10</v>
@@ -3145,10 +3293,10 @@
     </row>
     <row r="50" customFormat="1" spans="1:6">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>8</v>
@@ -3157,8 +3305,8 @@
         <v>9</v>
       </c>
       <c r="E50" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A50)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A50,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>10</v>
@@ -3166,10 +3314,10 @@
     </row>
     <row r="51" customFormat="1" spans="1:6">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>8</v>
@@ -3178,8 +3326,8 @@
         <v>9</v>
       </c>
       <c r="E51" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A51)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A51,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>10</v>
@@ -3187,10 +3335,10 @@
     </row>
     <row r="52" customFormat="1" spans="1:6">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>8</v>
@@ -3199,8 +3347,8 @@
         <v>9</v>
       </c>
       <c r="E52" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A52)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A52,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>10</v>
@@ -3208,10 +3356,10 @@
     </row>
     <row r="53" customFormat="1" spans="1:6">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>8</v>
@@ -3220,7 +3368,7 @@
         <v>9</v>
       </c>
       <c r="E53" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A53)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A53,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F53" s="4" t="s">
@@ -3229,10 +3377,10 @@
     </row>
     <row r="54" customFormat="1" spans="1:6">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
@@ -3241,7 +3389,7 @@
         <v>9</v>
       </c>
       <c r="E54" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A54)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A54,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F54" s="4" t="s">
@@ -3250,10 +3398,10 @@
     </row>
     <row r="55" customFormat="1" spans="1:6">
       <c r="A55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>8</v>
@@ -3262,8 +3410,8 @@
         <v>9</v>
       </c>
       <c r="E55" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A55)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A55,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>10</v>
@@ -3271,10 +3419,10 @@
     </row>
     <row r="56" customFormat="1" spans="1:6">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>8</v>
@@ -3283,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="E56" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A56)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A56,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F56" s="4" t="s">
@@ -3292,10 +3440,10 @@
     </row>
     <row r="57" customFormat="1" spans="1:6">
       <c r="A57" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>8</v>
@@ -3304,7 +3452,7 @@
         <v>9</v>
       </c>
       <c r="E57" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A57)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A57,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F57" s="4" t="s">
@@ -3313,10 +3461,10 @@
     </row>
     <row r="58" customFormat="1" spans="1:6">
       <c r="A58" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>8</v>
@@ -3325,7 +3473,7 @@
         <v>9</v>
       </c>
       <c r="E58" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A58)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A58,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F58" s="4" t="s">
@@ -3334,10 +3482,10 @@
     </row>
     <row r="59" customFormat="1" spans="1:6">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>8</v>
@@ -3346,8 +3494,8 @@
         <v>9</v>
       </c>
       <c r="E59" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A59)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A59,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>10</v>
@@ -3355,10 +3503,10 @@
     </row>
     <row r="60" customFormat="1" spans="1:6">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>8</v>
@@ -3367,8 +3515,8 @@
         <v>9</v>
       </c>
       <c r="E60" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A60)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A60,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>10</v>
@@ -3376,10 +3524,10 @@
     </row>
     <row r="61" customFormat="1" spans="1:6">
       <c r="A61" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>8</v>
@@ -3388,8 +3536,8 @@
         <v>9</v>
       </c>
       <c r="E61" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A61)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A61,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>10</v>
@@ -3397,10 +3545,10 @@
     </row>
     <row r="62" customFormat="1" spans="1:6">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>8</v>
@@ -3409,8 +3557,8 @@
         <v>9</v>
       </c>
       <c r="E62" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A62)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A62,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>10</v>
@@ -3418,10 +3566,10 @@
     </row>
     <row r="63" customFormat="1" spans="1:6">
       <c r="A63" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>8</v>
@@ -3430,8 +3578,8 @@
         <v>9</v>
       </c>
       <c r="E63" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A63)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A63,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>10</v>
@@ -3439,10 +3587,10 @@
     </row>
     <row r="64" customFormat="1" spans="1:6">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>8</v>
@@ -3451,7 +3599,7 @@
         <v>9</v>
       </c>
       <c r="E64" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A64)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A64,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F64" s="4" t="s">
@@ -3460,10 +3608,10 @@
     </row>
     <row r="65" customFormat="1" spans="1:6">
       <c r="A65" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>8</v>
@@ -3472,7 +3620,7 @@
         <v>9</v>
       </c>
       <c r="E65" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A65)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A65,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F65" s="4" t="s">
@@ -3481,10 +3629,10 @@
     </row>
     <row r="66" customFormat="1" spans="1:6">
       <c r="A66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>8</v>
@@ -3493,7 +3641,7 @@
         <v>9</v>
       </c>
       <c r="E66" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A66)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A66,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F66" s="4" t="s">
@@ -3502,10 +3650,10 @@
     </row>
     <row r="67" customFormat="1" spans="1:6">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>8</v>
@@ -3514,8 +3662,8 @@
         <v>9</v>
       </c>
       <c r="E67" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A67)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A67,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>10</v>
@@ -3523,10 +3671,10 @@
     </row>
     <row r="68" customFormat="1" spans="1:6">
       <c r="A68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>8</v>
@@ -3535,7 +3683,7 @@
         <v>9</v>
       </c>
       <c r="E68" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A68)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A68,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F68" s="4" t="s">
@@ -3544,10 +3692,10 @@
     </row>
     <row r="69" customFormat="1" spans="1:6">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>8</v>
@@ -3556,7 +3704,7 @@
         <v>9</v>
       </c>
       <c r="E69" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A69)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A69,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F69" s="4" t="s">
@@ -3565,10 +3713,10 @@
     </row>
     <row r="70" customFormat="1" spans="1:6">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>8</v>
@@ -3577,7 +3725,7 @@
         <v>9</v>
       </c>
       <c r="E70" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A70)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A70,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F70" s="4" t="s">
@@ -3586,10 +3734,10 @@
     </row>
     <row r="71" customFormat="1" spans="1:6">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>8</v>
@@ -3598,7 +3746,7 @@
         <v>9</v>
       </c>
       <c r="E71" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A71)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A71,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F71" s="4" t="s">
@@ -3607,10 +3755,10 @@
     </row>
     <row r="72" customFormat="1" spans="1:6">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>8</v>
@@ -3619,7 +3767,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A72)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A72,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F72" s="4" t="s">
@@ -3628,10 +3776,10 @@
     </row>
     <row r="73" customFormat="1" spans="1:6">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>8</v>
@@ -3640,8 +3788,8 @@
         <v>9</v>
       </c>
       <c r="E73" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A73)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A73,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>10</v>
@@ -3649,10 +3797,10 @@
     </row>
     <row r="74" customFormat="1" spans="1:6">
       <c r="A74" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>8</v>
@@ -3661,7 +3809,7 @@
         <v>9</v>
       </c>
       <c r="E74" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A74)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A74,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -3670,10 +3818,10 @@
     </row>
     <row r="75" customFormat="1" spans="1:6">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>8</v>
@@ -3682,8 +3830,8 @@
         <v>9</v>
       </c>
       <c r="E75" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A75)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A75,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>10</v>
@@ -3691,10 +3839,10 @@
     </row>
     <row r="76" customFormat="1" spans="1:6">
       <c r="A76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>8</v>
@@ -3703,7 +3851,7 @@
         <v>9</v>
       </c>
       <c r="E76" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A76)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A76,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F76" s="4" t="s">
@@ -3712,10 +3860,10 @@
     </row>
     <row r="77" customFormat="1" spans="1:6">
       <c r="A77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>8</v>
@@ -3724,7 +3872,7 @@
         <v>9</v>
       </c>
       <c r="E77" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A77)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A77,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F77" s="4" t="s">
@@ -3733,10 +3881,10 @@
     </row>
     <row r="78" customFormat="1" spans="1:6">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>8</v>
@@ -3745,7 +3893,7 @@
         <v>9</v>
       </c>
       <c r="E78" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A78)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A78,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F78" s="4" t="s">
@@ -3754,10 +3902,10 @@
     </row>
     <row r="79" customFormat="1" spans="1:6">
       <c r="A79" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>8</v>
@@ -3766,7 +3914,7 @@
         <v>9</v>
       </c>
       <c r="E79" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A79)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A79,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F79" s="4" t="s">
@@ -3775,10 +3923,10 @@
     </row>
     <row r="80" customFormat="1" spans="1:6">
       <c r="A80" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>8</v>
@@ -3787,7 +3935,7 @@
         <v>9</v>
       </c>
       <c r="E80" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A80)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A80,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F80" s="4" t="s">
@@ -3796,10 +3944,10 @@
     </row>
     <row r="81" customFormat="1" spans="1:6">
       <c r="A81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>8</v>
@@ -3808,8 +3956,8 @@
         <v>9</v>
       </c>
       <c r="E81" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A81)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A81,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>10</v>
@@ -3817,10 +3965,10 @@
     </row>
     <row r="82" customFormat="1" spans="1:6">
       <c r="A82" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>8</v>
@@ -3829,8 +3977,8 @@
         <v>9</v>
       </c>
       <c r="E82" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A82)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A82,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>10</v>
@@ -3838,10 +3986,10 @@
     </row>
     <row r="83" customFormat="1" spans="1:6">
       <c r="A83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>8</v>
@@ -3850,8 +3998,8 @@
         <v>9</v>
       </c>
       <c r="E83" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A83)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A83,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>10</v>
@@ -3859,10 +4007,10 @@
     </row>
     <row r="84" customFormat="1" spans="1:6">
       <c r="A84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>8</v>
@@ -3871,7 +4019,7 @@
         <v>9</v>
       </c>
       <c r="E84" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A84)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A84,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F84" s="4" t="s">
@@ -3880,10 +4028,10 @@
     </row>
     <row r="85" customFormat="1" spans="1:6">
       <c r="A85" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>8</v>
@@ -3892,8 +4040,8 @@
         <v>9</v>
       </c>
       <c r="E85" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A85)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A85,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>10</v>
@@ -3901,10 +4049,10 @@
     </row>
     <row r="86" customFormat="1" spans="1:6">
       <c r="A86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>8</v>
@@ -3913,8 +4061,8 @@
         <v>9</v>
       </c>
       <c r="E86" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A86)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A86,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>10</v>
@@ -3922,10 +4070,10 @@
     </row>
     <row r="87" customFormat="1" spans="1:6">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>8</v>
@@ -3934,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="E87" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A87)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A87,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F87" s="4" t="s">
@@ -3943,10 +4091,10 @@
     </row>
     <row r="88" customFormat="1" spans="1:6">
       <c r="A88" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>8</v>
@@ -3955,8 +4103,8 @@
         <v>9</v>
       </c>
       <c r="E88" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A88)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A88,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>10</v>
@@ -3964,10 +4112,10 @@
     </row>
     <row r="89" customFormat="1" spans="1:6">
       <c r="A89" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>8</v>
@@ -3976,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="E89" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A89)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A89,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F89" s="4" t="s">
@@ -3985,10 +4133,10 @@
     </row>
     <row r="90" customFormat="1" spans="1:6">
       <c r="A90" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>8</v>
@@ -3997,7 +4145,7 @@
         <v>9</v>
       </c>
       <c r="E90" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A90)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A90,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F90" s="4" t="s">
@@ -4006,10 +4154,10 @@
     </row>
     <row r="91" customFormat="1" spans="1:6">
       <c r="A91" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>8</v>
@@ -4018,7 +4166,7 @@
         <v>9</v>
       </c>
       <c r="E91" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A91)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A91,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F91" s="4" t="s">
@@ -4027,10 +4175,10 @@
     </row>
     <row r="92" customFormat="1" spans="1:6">
       <c r="A92" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>8</v>
@@ -4039,7 +4187,7 @@
         <v>9</v>
       </c>
       <c r="E92" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A92)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A92,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F92" s="4" t="s">
@@ -4048,10 +4196,10 @@
     </row>
     <row r="93" customFormat="1" spans="1:6">
       <c r="A93" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>8</v>
@@ -4060,7 +4208,7 @@
         <v>9</v>
       </c>
       <c r="E93" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A93)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A93,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F93" s="4" t="s">
@@ -4069,10 +4217,10 @@
     </row>
     <row r="94" customFormat="1" spans="1:6">
       <c r="A94" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>8</v>
@@ -4081,7 +4229,7 @@
         <v>9</v>
       </c>
       <c r="E94" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A94)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A94,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F94" s="4" t="s">
@@ -4090,10 +4238,10 @@
     </row>
     <row r="95" customFormat="1" spans="1:6">
       <c r="A95" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>8</v>
@@ -4102,7 +4250,7 @@
         <v>9</v>
       </c>
       <c r="E95" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A95)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A95,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F95" s="4" t="s">
@@ -4111,10 +4259,10 @@
     </row>
     <row r="96" customFormat="1" spans="1:6">
       <c r="A96" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>8</v>
@@ -4123,7 +4271,7 @@
         <v>9</v>
       </c>
       <c r="E96" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A96)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A96,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F96" s="4" t="s">
@@ -4132,10 +4280,10 @@
     </row>
     <row r="97" customFormat="1" spans="1:6">
       <c r="A97" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>8</v>
@@ -4144,7 +4292,7 @@
         <v>9</v>
       </c>
       <c r="E97" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A97)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A97,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F97" s="4" t="s">
@@ -4153,10 +4301,10 @@
     </row>
     <row r="98" customFormat="1" spans="1:6">
       <c r="A98" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>8</v>
@@ -4165,7 +4313,7 @@
         <v>9</v>
       </c>
       <c r="E98" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A98)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A98,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F98" s="4" t="s">
@@ -4174,10 +4322,10 @@
     </row>
     <row r="99" customFormat="1" spans="1:6">
       <c r="A99" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>8</v>
@@ -4186,7 +4334,7 @@
         <v>9</v>
       </c>
       <c r="E99" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A99)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A99,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F99" s="4" t="s">
@@ -4195,10 +4343,10 @@
     </row>
     <row r="100" customFormat="1" spans="1:6">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>8</v>
@@ -4207,8 +4355,8 @@
         <v>9</v>
       </c>
       <c r="E100" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A100)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A100,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>10</v>
@@ -4216,10 +4364,10 @@
     </row>
     <row r="101" customFormat="1" spans="1:6">
       <c r="A101" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>8</v>
@@ -4228,8 +4376,8 @@
         <v>9</v>
       </c>
       <c r="E101" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A101)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A101,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>10</v>
@@ -4237,10 +4385,10 @@
     </row>
     <row r="102" customFormat="1" spans="1:6">
       <c r="A102" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>8</v>
@@ -4249,8 +4397,8 @@
         <v>9</v>
       </c>
       <c r="E102" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A102)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A102,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>10</v>
@@ -4258,10 +4406,10 @@
     </row>
     <row r="103" customFormat="1" spans="1:6">
       <c r="A103" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>8</v>
@@ -4270,8 +4418,8 @@
         <v>9</v>
       </c>
       <c r="E103" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A103)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A103,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>10</v>
@@ -4279,10 +4427,10 @@
     </row>
     <row r="104" customFormat="1" spans="1:6">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>8</v>
@@ -4291,8 +4439,8 @@
         <v>9</v>
       </c>
       <c r="E104" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A104)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A104,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>10</v>
@@ -4300,10 +4448,10 @@
     </row>
     <row r="105" customFormat="1" spans="1:6">
       <c r="A105" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>8</v>
@@ -4312,7 +4460,7 @@
         <v>9</v>
       </c>
       <c r="E105" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A105)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A105,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F105" s="4" t="s">
@@ -4321,10 +4469,10 @@
     </row>
     <row r="106" customFormat="1" spans="1:6">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>8</v>
@@ -4332,9 +4480,8 @@
       <c r="D106" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E106" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A106)&gt;0,"on","off")</f>
-        <v>on</v>
+      <c r="E106" t="s">
+        <v>85</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>10</v>
@@ -4342,10 +4489,10 @@
     </row>
     <row r="107" customFormat="1" spans="1:6">
       <c r="A107" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>8</v>
@@ -4353,9 +4500,8 @@
       <c r="D107" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E107" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A107)&gt;0,"on","off")</f>
-        <v>on</v>
+      <c r="E107" t="s">
+        <v>85</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>10</v>
@@ -4363,10 +4509,10 @@
     </row>
     <row r="108" customFormat="1" spans="1:6">
       <c r="A108" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>8</v>
@@ -4375,8 +4521,8 @@
         <v>9</v>
       </c>
       <c r="E108" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A108)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A108,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>10</v>
@@ -4384,10 +4530,10 @@
     </row>
     <row r="109" customFormat="1" spans="1:6">
       <c r="A109" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>8</v>
@@ -4396,8 +4542,8 @@
         <v>9</v>
       </c>
       <c r="E109" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A109)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A109,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>10</v>
@@ -4405,10 +4551,10 @@
     </row>
     <row r="110" customFormat="1" spans="1:6">
       <c r="A110" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>8</v>
@@ -4417,8 +4563,8 @@
         <v>9</v>
       </c>
       <c r="E110" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A110)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A110,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>10</v>
@@ -4426,10 +4572,10 @@
     </row>
     <row r="111" customFormat="1" spans="1:6">
       <c r="A111" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>8</v>
@@ -4438,7 +4584,7 @@
         <v>9</v>
       </c>
       <c r="E111" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A111)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A111,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F111" s="4" t="s">
@@ -4447,10 +4593,10 @@
     </row>
     <row r="112" customFormat="1" spans="1:6">
       <c r="A112" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>8</v>
@@ -4459,8 +4605,8 @@
         <v>9</v>
       </c>
       <c r="E112" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A112)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A112,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>10</v>
@@ -4468,10 +4614,10 @@
     </row>
     <row r="113" customFormat="1" spans="1:6">
       <c r="A113" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>8</v>
@@ -4480,8 +4626,8 @@
         <v>9</v>
       </c>
       <c r="E113" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A113)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A113,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>10</v>
@@ -4489,10 +4635,10 @@
     </row>
     <row r="114" customFormat="1" spans="1:6">
       <c r="A114" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>8</v>
@@ -4501,8 +4647,8 @@
         <v>9</v>
       </c>
       <c r="E114" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A114)&gt;0,"on","off")</f>
-        <v>on</v>
+        <f>IF(ISNUMBER(MATCH(A114,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>10</v>
@@ -4510,10 +4656,10 @@
     </row>
     <row r="115" customFormat="1" spans="1:6">
       <c r="A115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>8</v>
@@ -4522,7 +4668,7 @@
         <v>9</v>
       </c>
       <c r="E115" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A115)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A115,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F115" s="4" t="s">
@@ -4531,10 +4677,10 @@
     </row>
     <row r="116" customFormat="1" spans="1:6">
       <c r="A116" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>8</v>
@@ -4543,7 +4689,7 @@
         <v>9</v>
       </c>
       <c r="E116" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A116)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A116,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F116" s="4" t="s">
@@ -4552,10 +4698,10 @@
     </row>
     <row r="117" customFormat="1" spans="1:6">
       <c r="A117" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>8</v>
@@ -4564,7 +4710,7 @@
         <v>9</v>
       </c>
       <c r="E117" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A117)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A117,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F117" s="4" t="s">
@@ -4573,10 +4719,10 @@
     </row>
     <row r="118" customFormat="1" spans="1:6">
       <c r="A118" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>8</v>
@@ -4585,7 +4731,7 @@
         <v>9</v>
       </c>
       <c r="E118" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A118)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A118,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F118" s="4" t="s">
@@ -4594,10 +4740,10 @@
     </row>
     <row r="119" customFormat="1" spans="1:6">
       <c r="A119" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>8</v>
@@ -4606,8 +4752,8 @@
         <v>9</v>
       </c>
       <c r="E119" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A119)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A119,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>10</v>
@@ -4615,10 +4761,10 @@
     </row>
     <row r="120" customFormat="1" spans="1:6">
       <c r="A120" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>8</v>
@@ -4627,7 +4773,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A120)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A120,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F120" s="4" t="s">
@@ -4636,10 +4782,10 @@
     </row>
     <row r="121" customFormat="1" spans="1:6">
       <c r="A121" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>8</v>
@@ -4648,7 +4794,7 @@
         <v>9</v>
       </c>
       <c r="E121" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A121)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A121,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F121" s="4" t="s">
@@ -4657,10 +4803,10 @@
     </row>
     <row r="122" customFormat="1" spans="1:6">
       <c r="A122" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>8</v>
@@ -4669,7 +4815,7 @@
         <v>9</v>
       </c>
       <c r="E122" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A122)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A122,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F122" s="4" t="s">
@@ -4678,10 +4824,10 @@
     </row>
     <row r="123" customFormat="1" spans="1:6">
       <c r="A123" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>8</v>
@@ -4690,8 +4836,8 @@
         <v>9</v>
       </c>
       <c r="E123" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A123)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A123,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>10</v>
@@ -4699,10 +4845,10 @@
     </row>
     <row r="124" customFormat="1" spans="1:6">
       <c r="A124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>8</v>
@@ -4710,9 +4856,8 @@
       <c r="D124" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E124" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A124)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E124" t="s">
+        <v>85</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>10</v>
@@ -4720,10 +4865,10 @@
     </row>
     <row r="125" customFormat="1" spans="1:6">
       <c r="A125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>8</v>
@@ -4731,9 +4876,8 @@
       <c r="D125" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E125" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A125)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E125" t="s">
+        <v>85</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>10</v>
@@ -4741,10 +4885,10 @@
     </row>
     <row r="126" customFormat="1" spans="1:6">
       <c r="A126" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>8</v>
@@ -4753,7 +4897,7 @@
         <v>9</v>
       </c>
       <c r="E126" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A126)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A126,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F126" s="4" t="s">
@@ -4762,10 +4906,10 @@
     </row>
     <row r="127" customFormat="1" spans="1:6">
       <c r="A127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>8</v>
@@ -4774,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="E127" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A127)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A127,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F127" s="4" t="s">
@@ -4783,10 +4927,10 @@
     </row>
     <row r="128" customFormat="1" spans="1:6">
       <c r="A128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>8</v>
@@ -4795,7 +4939,7 @@
         <v>9</v>
       </c>
       <c r="E128" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A128)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A128,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
       <c r="F128" s="4" t="s">
@@ -4804,10 +4948,10 @@
     </row>
     <row r="129" customFormat="1" spans="1:6">
       <c r="A129" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>8</v>
@@ -4815,9 +4959,8 @@
       <c r="D129" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E129" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A129)&gt;0,"on","off")</f>
-        <v>on</v>
+      <c r="E129" t="s">
+        <v>85</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>10</v>
@@ -4825,10 +4968,10 @@
     </row>
     <row r="130" customFormat="1" spans="1:6">
       <c r="A130" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>8</v>
@@ -4836,9 +4979,8 @@
       <c r="D130" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E130" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A130)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E130" t="s">
+        <v>85</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>10</v>
@@ -4846,10 +4988,10 @@
     </row>
     <row r="131" customFormat="1" spans="1:6">
       <c r="A131" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>8</v>
@@ -4857,9 +4999,8 @@
       <c r="D131" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E131" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A131)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E131" t="s">
+        <v>85</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>10</v>
@@ -4867,10 +5008,10 @@
     </row>
     <row r="132" customFormat="1" spans="1:6">
       <c r="A132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>8</v>
@@ -4879,7 +5020,7 @@
         <v>9</v>
       </c>
       <c r="E132" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A132)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A132,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F132" s="4" t="s">
@@ -4888,10 +5029,10 @@
     </row>
     <row r="133" customFormat="1" spans="1:6">
       <c r="A133" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>8</v>
@@ -4900,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="E133" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A133)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A133,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F133" s="4" t="s">
@@ -4909,10 +5050,10 @@
     </row>
     <row r="134" customFormat="1" spans="1:6">
       <c r="A134" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C134" s="4" t="s">
         <v>8</v>
@@ -4921,8 +5062,8 @@
         <v>9</v>
       </c>
       <c r="E134" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A134)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A134,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>10</v>
@@ -4930,10 +5071,10 @@
     </row>
     <row r="135" customFormat="1" spans="1:6">
       <c r="A135" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>8</v>
@@ -4942,7 +5083,7 @@
         <v>9</v>
       </c>
       <c r="E135" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A135)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A135,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F135" s="4" t="s">
@@ -4951,19 +5092,19 @@
     </row>
     <row r="136" customFormat="1" spans="1:6">
       <c r="A136" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A136)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A136,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F136" s="4" t="s">
@@ -4972,10 +5113,10 @@
     </row>
     <row r="137" customFormat="1" spans="1:6">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>8</v>
@@ -4984,7 +5125,7 @@
         <v>9</v>
       </c>
       <c r="E137" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A137)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A137,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F137" s="4" t="s">
@@ -4993,10 +5134,10 @@
     </row>
     <row r="138" customFormat="1" spans="1:6">
       <c r="A138" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>8</v>
@@ -5005,8 +5146,8 @@
         <v>9</v>
       </c>
       <c r="E138" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A138)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A138,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>10</v>
@@ -5014,10 +5155,10 @@
     </row>
     <row r="139" customFormat="1" spans="1:6">
       <c r="A139" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>8</v>
@@ -5026,8 +5167,8 @@
         <v>9</v>
       </c>
       <c r="E139" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A139)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A139,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>10</v>
@@ -5035,10 +5176,10 @@
     </row>
     <row r="140" customFormat="1" spans="1:6">
       <c r="A140" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>8</v>
@@ -5046,9 +5187,8 @@
       <c r="D140" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E140" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A140)&gt;0,"on","off")</f>
-        <v>off</v>
+      <c r="E140" t="s">
+        <v>85</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>10</v>
@@ -5056,10 +5196,10 @@
     </row>
     <row r="141" customFormat="1" spans="1:6">
       <c r="A141" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>8</v>
@@ -5068,8 +5208,8 @@
         <v>9</v>
       </c>
       <c r="E141" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A141)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A141,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>10</v>
@@ -5077,10 +5217,10 @@
     </row>
     <row r="142" customFormat="1" spans="1:6">
       <c r="A142" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>8</v>
@@ -5089,8 +5229,8 @@
         <v>9</v>
       </c>
       <c r="E142" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A142)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A142,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>10</v>
@@ -5098,10 +5238,10 @@
     </row>
     <row r="143" customFormat="1" spans="1:6">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>8</v>
@@ -5110,8 +5250,8 @@
         <v>9</v>
       </c>
       <c r="E143" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A143)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A143,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>10</v>
@@ -5119,10 +5259,10 @@
     </row>
     <row r="144" customFormat="1" spans="1:6">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>8</v>
@@ -5131,8 +5271,8 @@
         <v>9</v>
       </c>
       <c r="E144" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A144)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A144,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>10</v>
@@ -5140,10 +5280,10 @@
     </row>
     <row r="145" customFormat="1" spans="1:6">
       <c r="A145" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>8</v>
@@ -5152,8 +5292,8 @@
         <v>9</v>
       </c>
       <c r="E145" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A145)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A145,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>10</v>
@@ -5161,10 +5301,10 @@
     </row>
     <row r="146" customFormat="1" spans="1:6">
       <c r="A146" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>8</v>
@@ -5173,8 +5313,8 @@
         <v>9</v>
       </c>
       <c r="E146" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A146)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A146,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>10</v>
@@ -5182,10 +5322,10 @@
     </row>
     <row r="147" customFormat="1" spans="1:6">
       <c r="A147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>8</v>
@@ -5194,7 +5334,7 @@
         <v>9</v>
       </c>
       <c r="E147" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A147)&gt;0,"on","off")</f>
+        <f>IF(ISNUMBER(MATCH(A147,Sheet3!$A:$A,0)),"on","off")</f>
         <v>on</v>
       </c>
       <c r="F147" s="4" t="s">
@@ -5203,10 +5343,10 @@
     </row>
     <row r="148" customFormat="1" spans="1:6">
       <c r="A148" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>8</v>
@@ -5215,8 +5355,8 @@
         <v>9</v>
       </c>
       <c r="E148" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A148)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A148,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>10</v>
@@ -5224,10 +5364,10 @@
     </row>
     <row r="149" customFormat="1" spans="1:6">
       <c r="A149" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>8</v>
@@ -5236,8 +5376,8 @@
         <v>9</v>
       </c>
       <c r="E149" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A149)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A149,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>10</v>
@@ -5245,10 +5385,10 @@
     </row>
     <row r="150" customFormat="1" spans="1:6">
       <c r="A150" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>8</v>
@@ -5257,8 +5397,8 @@
         <v>9</v>
       </c>
       <c r="E150" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A150)&gt;0,"on","off")</f>
-        <v>off</v>
+        <f>IF(ISNUMBER(MATCH(A150,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>10</v>
@@ -5266,58 +5406,701 @@
     </row>
     <row r="151" customFormat="1" spans="1:6">
       <c r="A151" t="s">
+        <v>307</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="str">
+        <f>IF(ISNUMBER(MATCH(A151,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:6">
+      <c r="A152" t="s">
+        <v>309</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="str">
+        <f>IF(ISNUMBER(MATCH(A152,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>310</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="str">
+        <f>IF(ISNUMBER(MATCH(A153,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>311</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="str">
+        <f>IF(ISNUMBER(MATCH(A154,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="str">
+        <f>IF(ISNUMBER(MATCH(A155,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="str">
+        <f>IF(ISNUMBER(MATCH(A156,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>314</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="str">
+        <f>IF(ISNUMBER(MATCH(A157,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>315</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" t="str">
+        <f>IF(ISNUMBER(MATCH(A158,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F158" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="str">
+        <f>IF(ISNUMBER(MATCH(A159,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F159" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" t="str">
+        <f>IF(ISNUMBER(MATCH(A160,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F160" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="str">
+        <f>IF(ISNUMBER(MATCH(A161,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F161" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>319</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="str">
+        <f>IF(ISNUMBER(MATCH(A162,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F162" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>320</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" t="str">
+        <f>IF(ISNUMBER(MATCH(A163,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F163" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>321</v>
+      </c>
+      <c r="B164" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B151" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="str">
-        <f>IF(COUNTIF(Sheet2!$A:$A,A151)&gt;0,"on","off")</f>
-        <v>off</v>
-      </c>
-      <c r="F151" s="4" t="s">
+      <c r="C164" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" t="str">
+        <f>IF(ISNUMBER(MATCH(A164,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F164" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>322</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="str">
+        <f>IF(ISNUMBER(MATCH(A165,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F165" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>323</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>85</v>
+      </c>
+      <c r="F166" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>325</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="str">
+        <f>IF(ISNUMBER(MATCH(A167,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F167" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>327</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="str">
+        <f>IF(ISNUMBER(MATCH(A168,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F168" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>329</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="str">
+        <f>IF(ISNUMBER(MATCH(A169,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" ht="15" customHeight="1" spans="1:6">
+      <c r="A170" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" t="s">
+        <v>85</v>
+      </c>
+      <c r="F170" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>333</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
+        <v>85</v>
+      </c>
+      <c r="F171" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>335</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>85</v>
+      </c>
+      <c r="F172" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>168</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>85</v>
+      </c>
+      <c r="F173" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>338</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>85</v>
+      </c>
+      <c r="F174" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>340</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>85</v>
+      </c>
+      <c r="F175" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>310</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" t="s">
+        <v>85</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>343</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" t="s">
+        <v>85</v>
+      </c>
+      <c r="F177" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>345</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" t="s">
+        <v>85</v>
+      </c>
+      <c r="F178" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>347</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
+        <v>85</v>
+      </c>
+      <c r="F179" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>349</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" t="s">
+        <v>85</v>
+      </c>
+      <c r="F180" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" customFormat="1" spans="1:6">
+      <c r="A181" t="s">
+        <v>351</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" t="s">
+        <v>85</v>
+      </c>
+      <c r="F181" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" customFormat="1" spans="1:6">
+      <c r="A182" t="s">
+        <v>353</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>85</v>
+      </c>
+      <c r="F182" s="4" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F151" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F181" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A149">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B149">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A149">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="A150">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B150">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="A151">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A150">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="B151">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="B152:B165">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A151">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="B166:B180">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B137 B139:B147 B152:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  <conditionalFormatting sqref="B1:B137 B139:B147 B181:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5335,47 +6118,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -5385,7 +6168,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -5395,77 +6178,77 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -5475,7 +6258,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -5485,32 +6268,32 @@
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -5520,57 +6303,57 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:1">
@@ -5580,17 +6363,17 @@
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="1:1">
@@ -5600,12 +6383,12 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:1">
@@ -5615,17 +6398,17 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -5636,299 +6419,578 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A806"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:B820"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="88" customWidth="1"/>
+    <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:1">
+    <row r="1" ht="15.15" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" ht="15.15" spans="1:1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="2" ht="15.15" hidden="1" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" ht="15.15" spans="1:1">
+      <c r="B2" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A2)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="3" ht="15.15" hidden="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" ht="15.15" spans="1:1">
+        <v>90</v>
+      </c>
+      <c r="B3" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A3)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" hidden="1" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:1">
+      <c r="B4" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A4)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" hidden="1" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" ht="15.15" spans="1:1">
+      <c r="B5" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A5)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="6" ht="15.15" hidden="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" ht="15.15" spans="1:1">
+        <v>112</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A6)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="7" ht="15.15" hidden="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" ht="15.15" spans="1:1">
+        <v>114</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A7)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="8" ht="15.15" hidden="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" ht="15.15" spans="1:1">
+        <v>168</v>
+      </c>
+      <c r="B8" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A8)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="9" ht="15.15" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="10" ht="15.15" spans="1:1">
+        <v>325</v>
+      </c>
+      <c r="B9" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A9)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" hidden="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:1">
+        <v>122</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A10)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" hidden="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" ht="15.15" spans="1:1">
+        <v>275</v>
+      </c>
+      <c r="B11" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A11)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" hidden="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:1">
+        <v>277</v>
+      </c>
+      <c r="B12" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A12)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" hidden="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" ht="29.55" spans="1:1">
+        <v>227</v>
+      </c>
+      <c r="B13" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A13)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="14" ht="29.55" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="15" ht="15.15" spans="1:1">
-      <c r="A15" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" ht="15.15" spans="1:1">
+        <v>360</v>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A14)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="15" ht="29.55" spans="1:2">
+      <c r="A15" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A15)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.15" hidden="1" spans="1:2">
       <c r="A16" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" ht="15.15" spans="1:1">
+        <v>251</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A16)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="17" ht="15.15" hidden="1" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="18" ht="15.15" spans="1:1">
+        <v>235</v>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A17)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="18" ht="15.15" hidden="1" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="19" ht="15.15" spans="1:1">
+        <v>237</v>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A18)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="19" ht="15.15" hidden="1" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="20" ht="15.15" spans="1:1">
+        <v>280</v>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A19)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.15" hidden="1" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" ht="15.15" spans="1:1">
+        <v>215</v>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A20)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="21" ht="15.15" hidden="1" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" ht="15.15" spans="1:1">
+        <v>271</v>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A21)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" hidden="1" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" ht="15.15" spans="1:1">
+        <v>282</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A22)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.15" hidden="1" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="24" ht="15.15" spans="1:1">
+        <v>290</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A23)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="24" ht="15.15" hidden="1" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="25" ht="15.15" spans="1:1">
+        <v>292</v>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A24)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" hidden="1" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="26" ht="15.15" spans="1:1">
+        <v>303</v>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A25)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="26" ht="15.15" hidden="1" spans="1:2">
       <c r="A26" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" ht="15.15" spans="1:1">
+      <c r="B26" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A26)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="27" ht="15.15" hidden="1" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="28" ht="15.15" spans="1:1">
+        <v>305</v>
+      </c>
+      <c r="B27" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A27)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="28" ht="15.15" hidden="1" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="29" ht="15.15" spans="1:1">
+        <v>307</v>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A28)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="29" ht="15.15" hidden="1" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="30" ht="15.15" spans="1:1">
+        <v>309</v>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A29)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="30" ht="15.15" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" ht="87.15" spans="1:1">
-      <c r="A31" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A30)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="31" ht="15.15" hidden="1" spans="1:2">
+      <c r="A31" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B31" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A31)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="32" ht="15.15" hidden="1" spans="1:2">
+      <c r="A32" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A32)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="33" ht="15.15" hidden="1" spans="1:2">
+      <c r="A33" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A33)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="34" ht="15.15" hidden="1" spans="1:2">
+      <c r="A34" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A34)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="35" ht="15.15" hidden="1" spans="1:2">
+      <c r="A35" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B35" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A35)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="36" ht="15.15" hidden="1" spans="1:2">
+      <c r="A36" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B36" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A36)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="37" ht="15.15" hidden="1" spans="1:2">
+      <c r="A37" s="2" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="32" ht="15.15" spans="1:1">
-      <c r="A32" s="2" t="s">
+      <c r="B37" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A37)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="38" ht="15.15" hidden="1" spans="1:2">
+      <c r="A38" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B38" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A38)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="39" ht="15.15" hidden="1" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B39" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A39)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="40" ht="15.15" hidden="1" spans="1:2">
+      <c r="A40" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B40" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A40)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="41" ht="15.15" hidden="1" spans="1:2">
+      <c r="A41" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B41" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A41)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="42" ht="15.15" hidden="1" spans="1:2">
+      <c r="A42" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B42" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A42)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="43" ht="15.15" hidden="1" spans="1:2">
+      <c r="A43" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A43)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="44" ht="15.15" hidden="1" spans="1:2">
+      <c r="A44" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B44" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A44)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="45" ht="87.15" hidden="1" spans="1:2">
+      <c r="A45" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B45" t="e">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A45)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="46" ht="15.15" hidden="1" spans="1:2">
+      <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="33" ht="15.15" spans="1:1">
-      <c r="A33" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="34" ht="15.15" spans="1:1">
-      <c r="A34" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="35" ht="15.15" spans="1:1">
-      <c r="A35" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="36" ht="15.15" spans="1:1">
-      <c r="A36" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="37" ht="15.15" spans="1:1">
-      <c r="A37" s="2" t="s">
+      <c r="B46" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A46)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="47" ht="15.15" hidden="1" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A47)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="48" ht="15.15" hidden="1" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A48)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="49" ht="15.15" hidden="1" spans="1:2">
+      <c r="A49" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A49)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="50" ht="15.15" hidden="1" spans="1:2">
+      <c r="A50" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B50" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A50)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="51" ht="15.15" hidden="1" spans="1:2">
+      <c r="A51" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" ht="15.15" spans="1:1">
-      <c r="A38" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="39" ht="15.15" spans="1:1">
-      <c r="A39" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="40" ht="15.15" spans="1:1">
-      <c r="A40" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="41" ht="15.15" spans="1:1">
-      <c r="A41" s="2" t="s">
+      <c r="B51" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A51)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="52" ht="15.15" hidden="1" spans="1:2">
+      <c r="A52" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A52)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="53" ht="15.15" hidden="1" spans="1:2">
+      <c r="A53" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A53)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="54" ht="15.15" hidden="1" spans="1:2">
+      <c r="A54" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A54)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="55" ht="15.15" hidden="1" spans="1:2">
+      <c r="A55" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="42" ht="15.15" spans="1:1">
-      <c r="A42" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="43" ht="15.15" spans="1:1">
-      <c r="A43" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="44" ht="15.15" spans="1:1">
-      <c r="A44" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="45" ht="15.15" spans="1:1">
-      <c r="A45" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="46" ht="15.15" spans="1:1">
-      <c r="A46" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47" ht="15.15" spans="1:1">
-      <c r="A47" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" ht="15.15" spans="1:1">
-      <c r="A48" s="2" t="s">
+      <c r="B55" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A55)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="56" ht="15.15" hidden="1" spans="1:2">
+      <c r="A56" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A56)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="57" ht="15.15" spans="1:2">
+      <c r="A57" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B57" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A57)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="58" ht="15.15" hidden="1" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B58" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A58)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="59" ht="15.15" hidden="1" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B59" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A59)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="60" ht="15.15" hidden="1" spans="1:2">
+      <c r="A60" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B60" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A60)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="61" ht="15.15" hidden="1" spans="1:2">
+      <c r="A61" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B61" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A61)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="62" ht="15.15" hidden="1" spans="1:2">
+      <c r="A62" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A62)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="63" ht="15.15" hidden="1" spans="1:2">
+      <c r="A63" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="49" ht="15.15" spans="1:1">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" ht="15.15" spans="1:1">
-      <c r="A50" s="2"/>
-    </row>
-    <row r="51" ht="15.15" spans="1:1">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="52" ht="15.15" spans="1:1">
-      <c r="A52" s="2"/>
-    </row>
-    <row r="53" ht="15.15" spans="1:1">
-      <c r="A53" s="2"/>
-    </row>
-    <row r="54" ht="15.15" spans="1:1">
-      <c r="A54" s="2"/>
-    </row>
-    <row r="55" ht="15.15" spans="1:1">
-      <c r="A55" s="2"/>
-    </row>
-    <row r="56" ht="15.15" spans="1:1">
-      <c r="A56" s="2"/>
-    </row>
-    <row r="57" ht="15.15" spans="1:1">
-      <c r="A57" s="2"/>
-    </row>
-    <row r="58" ht="15.15" spans="1:1">
-      <c r="A58" s="2"/>
-    </row>
-    <row r="59" ht="15.15" spans="1:1">
-      <c r="A59" s="2"/>
-    </row>
-    <row r="60" ht="15.15" spans="1:1">
-      <c r="A60" s="2"/>
-    </row>
-    <row r="61" ht="15.15" spans="1:1">
-      <c r="A61" s="2"/>
-    </row>
-    <row r="62" ht="15.15" spans="1:1">
-      <c r="A62" s="2"/>
-    </row>
-    <row r="63" ht="15.15" spans="1:1">
-      <c r="A63" s="2"/>
-    </row>
-    <row r="64" ht="15.15" spans="1:1">
+      <c r="B63" t="str">
+        <f>IF(COUNTIF(Sheet1!$A:$A,A63)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="64" ht="15.15" spans="1:2">
       <c r="A64" s="2"/>
     </row>
     <row r="65" ht="15.15" spans="1:1">
@@ -8157,7 +9219,57 @@
     <row r="806" ht="15.15" spans="1:1">
       <c r="A806" s="2"/>
     </row>
+    <row r="807" ht="15.15" spans="1:1">
+      <c r="A807" s="2"/>
+    </row>
+    <row r="808" ht="15.15" spans="1:1">
+      <c r="A808" s="2"/>
+    </row>
+    <row r="809" ht="15.15" spans="1:1">
+      <c r="A809" s="2"/>
+    </row>
+    <row r="810" ht="15.15" spans="1:1">
+      <c r="A810" s="2"/>
+    </row>
+    <row r="811" ht="15.15" spans="1:1">
+      <c r="A811" s="2"/>
+    </row>
+    <row r="812" ht="15.15" spans="1:1">
+      <c r="A812" s="2"/>
+    </row>
+    <row r="813" ht="15.15" spans="1:1">
+      <c r="A813" s="2"/>
+    </row>
+    <row r="814" ht="15.15" spans="1:1">
+      <c r="A814" s="2"/>
+    </row>
+    <row r="815" ht="15.15" spans="1:1">
+      <c r="A815" s="2"/>
+    </row>
+    <row r="816" ht="15.15" spans="1:1">
+      <c r="A816" s="2"/>
+    </row>
+    <row r="817" ht="15.15" spans="1:1">
+      <c r="A817" s="2"/>
+    </row>
+    <row r="818" ht="15.15" spans="1:1">
+      <c r="A818" s="2"/>
+    </row>
+    <row r="819" ht="15.15" spans="1:1">
+      <c r="A819" s="2"/>
+    </row>
+    <row r="820" ht="15.15" spans="1:1">
+      <c r="A820" s="2"/>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B63" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="equal" val="NE POSTOJI u Sheet1"/>
+      </customFilters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/testdata/configurationUAT/listForExecution.xlsx
+++ b/testdata/configurationUAT/listForExecution.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22728" windowHeight="9528"/>
+    <workbookView windowWidth="21648" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$182</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$B$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="382">
   <si>
     <t>TestName</t>
   </si>
@@ -74,6 +74,9 @@
     <t>C70765</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -290,9 +293,6 @@
     <t>C70802</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
   </si>
   <si>
@@ -1098,6 +1098,63 @@
   </si>
   <si>
     <t>C70931</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70932</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70933</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70934</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70935</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Multiple_Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70936</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Search_[WEB]</t>
+  </si>
+  <si>
+    <t>C70937</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Filter_By_Date_Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70938</t>
+  </si>
+  <si>
+    <t>C70939</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Header_Display_[WEB]</t>
+  </si>
+  <si>
+    <t>C70940</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Search_Option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70941</t>
   </si>
   <si>
     <t>Name</t>
@@ -1906,7 +1963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1926,6 +1983,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2258,7 +2318,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -2297,9 +2357,8 @@
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="str">
-        <f>IF(ISNUMBER(MATCH(A2,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E2" t="s">
+        <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>10</v>
@@ -2318,9 +2377,8 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="str">
-        <f>IF(ISNUMBER(MATCH(A3,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>10</v>
@@ -2328,10 +2386,10 @@
     </row>
     <row r="4" customFormat="1" spans="1:6">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
@@ -2339,9 +2397,8 @@
       <c r="D4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="str">
-        <f>IF(ISNUMBER(MATCH(A4,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>10</v>
@@ -2349,10 +2406,10 @@
     </row>
     <row r="5" customFormat="1" spans="1:6">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>8</v>
@@ -2360,9 +2417,8 @@
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="str">
-        <f>IF(ISNUMBER(MATCH(A5,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E5" t="s">
+        <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>10</v>
@@ -2370,10 +2426,10 @@
     </row>
     <row r="6" customFormat="1" spans="1:6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>8</v>
@@ -2381,9 +2437,8 @@
       <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="str">
-        <f>IF(ISNUMBER(MATCH(A6,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E6" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>10</v>
@@ -2391,10 +2446,10 @@
     </row>
     <row r="7" customFormat="1" spans="1:6">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
@@ -2402,9 +2457,8 @@
       <c r="D7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="str">
-        <f>IF(ISNUMBER(MATCH(A7,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E7" t="s">
+        <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>10</v>
@@ -2412,10 +2466,10 @@
     </row>
     <row r="8" customFormat="1" spans="1:6">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>8</v>
@@ -2423,9 +2477,8 @@
       <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" t="str">
-        <f>IF(ISNUMBER(MATCH(A8,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E8" t="s">
+        <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>10</v>
@@ -2433,10 +2486,10 @@
     </row>
     <row r="9" customFormat="1" spans="1:6">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>8</v>
@@ -2444,9 +2497,8 @@
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E9" t="str">
-        <f>IF(ISNUMBER(MATCH(A9,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E9" t="s">
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>10</v>
@@ -2454,10 +2506,10 @@
     </row>
     <row r="10" customFormat="1" spans="1:6">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
@@ -2465,9 +2517,8 @@
       <c r="D10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E10" t="str">
-        <f>IF(ISNUMBER(MATCH(A10,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E10" t="s">
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -2475,10 +2526,10 @@
     </row>
     <row r="11" customFormat="1" spans="1:6">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>8</v>
@@ -2486,9 +2537,8 @@
       <c r="D11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E11" t="str">
-        <f>IF(ISNUMBER(MATCH(A11,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E11" t="s">
+        <v>13</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -2496,10 +2546,10 @@
     </row>
     <row r="12" customFormat="1" spans="1:6">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
@@ -2507,9 +2557,8 @@
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" t="str">
-        <f>IF(ISNUMBER(MATCH(A12,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E12" t="s">
+        <v>10</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>10</v>
@@ -2517,10 +2566,10 @@
     </row>
     <row r="13" customFormat="1" spans="1:6">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
@@ -2528,9 +2577,8 @@
       <c r="D13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E13" t="str">
-        <f>IF(ISNUMBER(MATCH(A13,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E13" t="s">
+        <v>10</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>10</v>
@@ -2538,10 +2586,10 @@
     </row>
     <row r="14" customFormat="1" spans="1:6">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>8</v>
@@ -2549,9 +2597,8 @@
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" t="str">
-        <f>IF(ISNUMBER(MATCH(A14,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E14" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>10</v>
@@ -2559,10 +2606,10 @@
     </row>
     <row r="15" customFormat="1" spans="1:6">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>8</v>
@@ -2570,9 +2617,8 @@
       <c r="D15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E15" t="str">
-        <f>IF(ISNUMBER(MATCH(A15,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E15" t="s">
+        <v>10</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>10</v>
@@ -2580,10 +2626,10 @@
     </row>
     <row r="16" customFormat="1" spans="1:6">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>8</v>
@@ -2591,9 +2637,8 @@
       <c r="D16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E16" t="str">
-        <f>IF(ISNUMBER(MATCH(A16,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E16" t="s">
+        <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>10</v>
@@ -2601,10 +2646,10 @@
     </row>
     <row r="17" customFormat="1" spans="1:6">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>8</v>
@@ -2612,9 +2657,8 @@
       <c r="D17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E17" t="str">
-        <f>IF(ISNUMBER(MATCH(A17,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E17" t="s">
+        <v>10</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>10</v>
@@ -2622,10 +2666,10 @@
     </row>
     <row r="18" customFormat="1" spans="1:6">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>8</v>
@@ -2633,9 +2677,8 @@
       <c r="D18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E18" t="str">
-        <f>IF(ISNUMBER(MATCH(A18,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E18" t="s">
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>10</v>
@@ -2643,10 +2686,10 @@
     </row>
     <row r="19" customFormat="1" spans="1:6">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>8</v>
@@ -2654,9 +2697,8 @@
       <c r="D19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E19" t="str">
-        <f>IF(ISNUMBER(MATCH(A19,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E19" t="s">
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>10</v>
@@ -2664,10 +2706,10 @@
     </row>
     <row r="20" customFormat="1" spans="1:6">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>8</v>
@@ -2675,9 +2717,8 @@
       <c r="D20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E20" t="str">
-        <f>IF(ISNUMBER(MATCH(A20,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E20" t="s">
+        <v>10</v>
       </c>
       <c r="F20" t="s">
         <v>10</v>
@@ -2685,10 +2726,10 @@
     </row>
     <row r="21" customFormat="1" spans="1:6">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>8</v>
@@ -2696,9 +2737,8 @@
       <c r="D21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E21" t="str">
-        <f>IF(ISNUMBER(MATCH(A21,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E21" t="s">
+        <v>13</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -2706,10 +2746,10 @@
     </row>
     <row r="22" customFormat="1" spans="1:6">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>8</v>
@@ -2717,9 +2757,8 @@
       <c r="D22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E22" t="str">
-        <f>IF(ISNUMBER(MATCH(A22,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E22" t="s">
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>10</v>
@@ -2727,10 +2766,10 @@
     </row>
     <row r="23" customFormat="1" spans="1:6">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>8</v>
@@ -2738,9 +2777,8 @@
       <c r="D23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E23" t="str">
-        <f>IF(ISNUMBER(MATCH(A23,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E23" t="s">
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>10</v>
@@ -2748,10 +2786,10 @@
     </row>
     <row r="24" customFormat="1" spans="1:6">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>8</v>
@@ -2759,9 +2797,8 @@
       <c r="D24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E24" t="str">
-        <f>IF(ISNUMBER(MATCH(A24,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E24" t="s">
+        <v>13</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>10</v>
@@ -2769,10 +2806,10 @@
     </row>
     <row r="25" customFormat="1" spans="1:6">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>8</v>
@@ -2780,9 +2817,8 @@
       <c r="D25" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E25" t="str">
-        <f>IF(ISNUMBER(MATCH(A25,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E25" t="s">
+        <v>10</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>10</v>
@@ -2790,10 +2826,10 @@
     </row>
     <row r="26" customFormat="1" spans="1:6">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>8</v>
@@ -2801,9 +2837,8 @@
       <c r="D26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E26" t="str">
-        <f>IF(ISNUMBER(MATCH(A26,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E26" t="s">
+        <v>10</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>10</v>
@@ -2811,10 +2846,10 @@
     </row>
     <row r="27" customFormat="1" spans="1:6">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
@@ -2822,9 +2857,8 @@
       <c r="D27" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E27" t="str">
-        <f>IF(ISNUMBER(MATCH(A27,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E27" t="s">
+        <v>10</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>10</v>
@@ -2832,10 +2866,10 @@
     </row>
     <row r="28" customFormat="1" spans="1:6">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>8</v>
@@ -2843,9 +2877,8 @@
       <c r="D28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E28" t="str">
-        <f>IF(ISNUMBER(MATCH(A28,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E28" t="s">
+        <v>13</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>10</v>
@@ -2853,10 +2886,10 @@
     </row>
     <row r="29" customFormat="1" spans="1:6">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>8</v>
@@ -2864,9 +2897,8 @@
       <c r="D29" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E29" t="str">
-        <f>IF(ISNUMBER(MATCH(A29,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E29" t="s">
+        <v>13</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>10</v>
@@ -2874,10 +2906,10 @@
     </row>
     <row r="30" customFormat="1" spans="1:6">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>8</v>
@@ -2885,9 +2917,8 @@
       <c r="D30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E30" t="str">
-        <f>IF(ISNUMBER(MATCH(A30,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E30" t="s">
+        <v>13</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>10</v>
@@ -2895,10 +2926,10 @@
     </row>
     <row r="31" customFormat="1" spans="1:6">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>8</v>
@@ -2906,9 +2937,8 @@
       <c r="D31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E31" t="str">
-        <f>IF(ISNUMBER(MATCH(A31,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E31" t="s">
+        <v>10</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>10</v>
@@ -2916,10 +2946,10 @@
     </row>
     <row r="32" customFormat="1" spans="1:6">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>8</v>
@@ -2927,9 +2957,8 @@
       <c r="D32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E32" t="str">
-        <f>IF(ISNUMBER(MATCH(A32,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E32" t="s">
+        <v>10</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>10</v>
@@ -2937,10 +2966,10 @@
     </row>
     <row r="33" customFormat="1" spans="1:6">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
@@ -2948,9 +2977,8 @@
       <c r="D33" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E33" t="str">
-        <f>IF(ISNUMBER(MATCH(A33,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E33" t="s">
+        <v>10</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>10</v>
@@ -2958,10 +2986,10 @@
     </row>
     <row r="34" customFormat="1" spans="1:6">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>8</v>
@@ -2969,9 +2997,8 @@
       <c r="D34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E34" t="str">
-        <f>IF(ISNUMBER(MATCH(A34,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E34" t="s">
+        <v>10</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>10</v>
@@ -2979,10 +3006,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:6">
       <c r="A35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
@@ -2990,9 +3017,8 @@
       <c r="D35" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E35" t="str">
-        <f>IF(ISNUMBER(MATCH(A35,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E35" t="s">
+        <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>10</v>
@@ -3000,10 +3026,10 @@
     </row>
     <row r="36" customFormat="1" spans="1:6">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>8</v>
@@ -3011,9 +3037,8 @@
       <c r="D36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E36" t="str">
-        <f>IF(ISNUMBER(MATCH(A36,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E36" t="s">
+        <v>13</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>10</v>
@@ -3021,10 +3046,10 @@
     </row>
     <row r="37" customFormat="1" spans="1:6">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>8</v>
@@ -3032,9 +3057,8 @@
       <c r="D37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E37" t="str">
-        <f>IF(ISNUMBER(MATCH(A37,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E37" t="s">
+        <v>10</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>10</v>
@@ -3042,10 +3066,10 @@
     </row>
     <row r="38" customFormat="1" spans="1:6">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>8</v>
@@ -3053,9 +3077,8 @@
       <c r="D38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E38" t="str">
-        <f>IF(ISNUMBER(MATCH(A38,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E38" t="s">
+        <v>10</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>10</v>
@@ -3063,10 +3086,10 @@
     </row>
     <row r="39" customFormat="1" spans="1:6">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
@@ -3075,7 +3098,7 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>10</v>
@@ -3094,9 +3117,8 @@
       <c r="D40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E40" t="str">
-        <f>IF(ISNUMBER(MATCH(A40,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E40" t="s">
+        <v>13</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>10</v>
@@ -3115,9 +3137,8 @@
       <c r="D41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E41" t="str">
-        <f>IF(ISNUMBER(MATCH(A41,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E41" t="s">
+        <v>10</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>10</v>
@@ -3136,9 +3157,8 @@
       <c r="D42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E42" t="str">
-        <f>IF(ISNUMBER(MATCH(A42,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E42" t="s">
+        <v>13</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -3157,9 +3177,8 @@
       <c r="D43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E43" t="str">
-        <f>IF(ISNUMBER(MATCH(A43,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E43" t="s">
+        <v>13</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -3178,9 +3197,8 @@
       <c r="D44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E44" t="str">
-        <f>IF(ISNUMBER(MATCH(A44,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E44" t="s">
+        <v>10</v>
       </c>
       <c r="F44" t="s">
         <v>10</v>
@@ -3199,9 +3217,8 @@
       <c r="D45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E45" t="str">
-        <f>IF(ISNUMBER(MATCH(A45,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E45" t="s">
+        <v>10</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>10</v>
@@ -3220,9 +3237,8 @@
       <c r="D46" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E46" t="str">
-        <f>IF(ISNUMBER(MATCH(A46,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E46" t="s">
+        <v>10</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>10</v>
@@ -3241,9 +3257,8 @@
       <c r="D47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E47" t="str">
-        <f>IF(ISNUMBER(MATCH(A47,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E47" t="s">
+        <v>10</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>10</v>
@@ -3262,9 +3277,8 @@
       <c r="D48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E48" t="str">
-        <f>IF(ISNUMBER(MATCH(A48,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E48" t="s">
+        <v>13</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>10</v>
@@ -3283,9 +3297,8 @@
       <c r="D49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E49" t="str">
-        <f>IF(ISNUMBER(MATCH(A49,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E49" t="s">
+        <v>10</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>10</v>
@@ -3304,9 +3317,8 @@
       <c r="D50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E50" t="str">
-        <f>IF(ISNUMBER(MATCH(A50,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E50" t="s">
+        <v>13</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>10</v>
@@ -3325,9 +3337,8 @@
       <c r="D51" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E51" t="str">
-        <f>IF(ISNUMBER(MATCH(A51,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E51" t="s">
+        <v>10</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>10</v>
@@ -3346,9 +3357,8 @@
       <c r="D52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E52" t="str">
-        <f>IF(ISNUMBER(MATCH(A52,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E52" t="s">
+        <v>10</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>10</v>
@@ -3367,9 +3377,8 @@
       <c r="D53" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E53" t="str">
-        <f>IF(ISNUMBER(MATCH(A53,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E53" t="s">
+        <v>13</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>10</v>
@@ -3388,9 +3397,8 @@
       <c r="D54" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E54" t="str">
-        <f>IF(ISNUMBER(MATCH(A54,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E54" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>10</v>
@@ -3409,9 +3417,8 @@
       <c r="D55" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E55" t="str">
-        <f>IF(ISNUMBER(MATCH(A55,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E55" t="s">
+        <v>13</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>10</v>
@@ -3430,9 +3437,8 @@
       <c r="D56" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E56" t="str">
-        <f>IF(ISNUMBER(MATCH(A56,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E56" t="s">
+        <v>13</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>10</v>
@@ -3451,9 +3457,8 @@
       <c r="D57" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E57" t="str">
-        <f>IF(ISNUMBER(MATCH(A57,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E57" t="s">
+        <v>10</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>10</v>
@@ -3472,9 +3477,8 @@
       <c r="D58" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E58" t="str">
-        <f>IF(ISNUMBER(MATCH(A58,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E58" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>10</v>
@@ -3493,9 +3497,8 @@
       <c r="D59" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E59" t="str">
-        <f>IF(ISNUMBER(MATCH(A59,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E59" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>10</v>
@@ -3514,9 +3517,8 @@
       <c r="D60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E60" t="str">
-        <f>IF(ISNUMBER(MATCH(A60,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E60" t="s">
+        <v>10</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>10</v>
@@ -3535,9 +3537,8 @@
       <c r="D61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E61" t="str">
-        <f>IF(ISNUMBER(MATCH(A61,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E61" t="s">
+        <v>10</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>10</v>
@@ -3556,9 +3557,8 @@
       <c r="D62" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E62" t="str">
-        <f>IF(ISNUMBER(MATCH(A62,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E62" t="s">
+        <v>10</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>10</v>
@@ -3577,9 +3577,8 @@
       <c r="D63" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E63" t="str">
-        <f>IF(ISNUMBER(MATCH(A63,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E63" t="s">
+        <v>13</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>10</v>
@@ -3598,9 +3597,8 @@
       <c r="D64" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E64" t="str">
-        <f>IF(ISNUMBER(MATCH(A64,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E64" t="s">
+        <v>10</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>10</v>
@@ -3619,9 +3617,8 @@
       <c r="D65" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E65" t="str">
-        <f>IF(ISNUMBER(MATCH(A65,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E65" t="s">
+        <v>10</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>10</v>
@@ -3640,9 +3637,8 @@
       <c r="D66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E66" t="str">
-        <f>IF(ISNUMBER(MATCH(A66,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E66" t="s">
+        <v>10</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>10</v>
@@ -3661,9 +3657,8 @@
       <c r="D67" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E67" t="str">
-        <f>IF(ISNUMBER(MATCH(A67,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E67" t="s">
+        <v>13</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>10</v>
@@ -3682,9 +3677,8 @@
       <c r="D68" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E68" t="str">
-        <f>IF(ISNUMBER(MATCH(A68,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E68" t="s">
+        <v>13</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>10</v>
@@ -3703,9 +3697,8 @@
       <c r="D69" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E69" t="str">
-        <f>IF(ISNUMBER(MATCH(A69,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E69" t="s">
+        <v>10</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>10</v>
@@ -3724,9 +3717,8 @@
       <c r="D70" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E70" t="str">
-        <f>IF(ISNUMBER(MATCH(A70,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E70" t="s">
+        <v>10</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>10</v>
@@ -3745,9 +3737,8 @@
       <c r="D71" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E71" t="str">
-        <f>IF(ISNUMBER(MATCH(A71,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E71" t="s">
+        <v>10</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>10</v>
@@ -3766,9 +3757,8 @@
       <c r="D72" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E72" t="str">
-        <f>IF(ISNUMBER(MATCH(A72,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E72" t="s">
+        <v>10</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>10</v>
@@ -3787,9 +3777,8 @@
       <c r="D73" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E73" t="str">
-        <f>IF(ISNUMBER(MATCH(A73,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E73" t="s">
+        <v>10</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>10</v>
@@ -3808,9 +3797,8 @@
       <c r="D74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E74" t="str">
-        <f>IF(ISNUMBER(MATCH(A74,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E74" t="s">
+        <v>13</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>10</v>
@@ -3829,9 +3817,8 @@
       <c r="D75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E75" t="str">
-        <f>IF(ISNUMBER(MATCH(A75,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E75" t="s">
+        <v>10</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>10</v>
@@ -3850,9 +3837,8 @@
       <c r="D76" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E76" t="str">
-        <f>IF(ISNUMBER(MATCH(A76,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E76" t="s">
+        <v>13</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>10</v>
@@ -3871,9 +3857,8 @@
       <c r="D77" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E77" t="str">
-        <f>IF(ISNUMBER(MATCH(A77,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E77" t="s">
+        <v>13</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>10</v>
@@ -3892,9 +3877,8 @@
       <c r="D78" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E78" t="str">
-        <f>IF(ISNUMBER(MATCH(A78,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E78" t="s">
+        <v>13</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>10</v>
@@ -3913,9 +3897,8 @@
       <c r="D79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E79" t="str">
-        <f>IF(ISNUMBER(MATCH(A79,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E79" t="s">
+        <v>13</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>10</v>
@@ -3934,9 +3917,8 @@
       <c r="D80" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E80" t="str">
-        <f>IF(ISNUMBER(MATCH(A80,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E80" t="s">
+        <v>13</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>10</v>
@@ -3955,9 +3937,8 @@
       <c r="D81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E81" t="str">
-        <f>IF(ISNUMBER(MATCH(A81,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E81" t="s">
+        <v>13</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>10</v>
@@ -3976,9 +3957,8 @@
       <c r="D82" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E82" t="str">
-        <f>IF(ISNUMBER(MATCH(A82,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E82" t="s">
+        <v>10</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>10</v>
@@ -3997,9 +3977,8 @@
       <c r="D83" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E83" t="str">
-        <f>IF(ISNUMBER(MATCH(A83,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E83" t="s">
+        <v>10</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>10</v>
@@ -4018,9 +3997,8 @@
       <c r="D84" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E84" t="str">
-        <f>IF(ISNUMBER(MATCH(A84,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E84" t="s">
+        <v>13</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>10</v>
@@ -4039,9 +4017,8 @@
       <c r="D85" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E85" t="str">
-        <f>IF(ISNUMBER(MATCH(A85,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E85" t="s">
+        <v>10</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>10</v>
@@ -4060,9 +4037,8 @@
       <c r="D86" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E86" t="str">
-        <f>IF(ISNUMBER(MATCH(A86,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E86" t="s">
+        <v>10</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>10</v>
@@ -4081,9 +4057,8 @@
       <c r="D87" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E87" t="str">
-        <f>IF(ISNUMBER(MATCH(A87,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E87" t="s">
+        <v>10</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>10</v>
@@ -4102,9 +4077,8 @@
       <c r="D88" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E88" t="str">
-        <f>IF(ISNUMBER(MATCH(A88,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E88" t="s">
+        <v>13</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>10</v>
@@ -4123,9 +4097,8 @@
       <c r="D89" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E89" t="str">
-        <f>IF(ISNUMBER(MATCH(A89,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E89" t="s">
+        <v>10</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>10</v>
@@ -4144,9 +4117,8 @@
       <c r="D90" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E90" t="str">
-        <f>IF(ISNUMBER(MATCH(A90,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E90" t="s">
+        <v>10</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>10</v>
@@ -4165,9 +4137,8 @@
       <c r="D91" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E91" t="str">
-        <f>IF(ISNUMBER(MATCH(A91,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E91" t="s">
+        <v>13</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>10</v>
@@ -4186,9 +4157,8 @@
       <c r="D92" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E92" t="str">
-        <f>IF(ISNUMBER(MATCH(A92,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E92" t="s">
+        <v>13</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>10</v>
@@ -4207,9 +4177,8 @@
       <c r="D93" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E93" t="str">
-        <f>IF(ISNUMBER(MATCH(A93,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E93" t="s">
+        <v>10</v>
       </c>
       <c r="F93" s="4" t="s">
         <v>10</v>
@@ -4228,9 +4197,8 @@
       <c r="D94" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E94" t="str">
-        <f>IF(ISNUMBER(MATCH(A94,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E94" t="s">
+        <v>10</v>
       </c>
       <c r="F94" s="4" t="s">
         <v>10</v>
@@ -4249,9 +4217,8 @@
       <c r="D95" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E95" t="str">
-        <f>IF(ISNUMBER(MATCH(A95,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E95" t="s">
+        <v>10</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>10</v>
@@ -4270,9 +4237,8 @@
       <c r="D96" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E96" t="str">
-        <f>IF(ISNUMBER(MATCH(A96,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E96" t="s">
+        <v>10</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>10</v>
@@ -4291,9 +4257,8 @@
       <c r="D97" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E97" t="str">
-        <f>IF(ISNUMBER(MATCH(A97,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E97" t="s">
+        <v>10</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>10</v>
@@ -4312,9 +4277,8 @@
       <c r="D98" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E98" t="str">
-        <f>IF(ISNUMBER(MATCH(A98,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E98" t="s">
+        <v>10</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>10</v>
@@ -4333,9 +4297,8 @@
       <c r="D99" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E99" t="str">
-        <f>IF(ISNUMBER(MATCH(A99,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E99" t="s">
+        <v>10</v>
       </c>
       <c r="F99" s="4" t="s">
         <v>10</v>
@@ -4354,9 +4317,8 @@
       <c r="D100" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E100" t="str">
-        <f>IF(ISNUMBER(MATCH(A100,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E100" t="s">
+        <v>10</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>10</v>
@@ -4375,9 +4337,8 @@
       <c r="D101" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E101" t="str">
-        <f>IF(ISNUMBER(MATCH(A101,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E101" t="s">
+        <v>13</v>
       </c>
       <c r="F101" s="4" t="s">
         <v>10</v>
@@ -4396,9 +4357,8 @@
       <c r="D102" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E102" t="str">
-        <f>IF(ISNUMBER(MATCH(A102,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E102" t="s">
+        <v>10</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>10</v>
@@ -4417,9 +4377,8 @@
       <c r="D103" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E103" t="str">
-        <f>IF(ISNUMBER(MATCH(A103,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E103" t="s">
+        <v>10</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>10</v>
@@ -4438,9 +4397,8 @@
       <c r="D104" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E104" t="str">
-        <f>IF(ISNUMBER(MATCH(A104,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E104" t="s">
+        <v>10</v>
       </c>
       <c r="F104" s="4" t="s">
         <v>10</v>
@@ -4459,9 +4417,8 @@
       <c r="D105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E105" t="str">
-        <f>IF(ISNUMBER(MATCH(A105,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E105" t="s">
+        <v>13</v>
       </c>
       <c r="F105" s="4" t="s">
         <v>10</v>
@@ -4481,7 +4438,7 @@
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F106" s="4" t="s">
         <v>10</v>
@@ -4501,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>10</v>
@@ -4520,9 +4477,8 @@
       <c r="D108" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E108" t="str">
-        <f>IF(ISNUMBER(MATCH(A108,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E108" t="s">
+        <v>13</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>10</v>
@@ -4541,9 +4497,8 @@
       <c r="D109" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E109" t="str">
-        <f>IF(ISNUMBER(MATCH(A109,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E109" t="s">
+        <v>10</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>10</v>
@@ -4562,9 +4517,8 @@
       <c r="D110" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E110" t="str">
-        <f>IF(ISNUMBER(MATCH(A110,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E110" t="s">
+        <v>10</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>10</v>
@@ -4583,9 +4537,8 @@
       <c r="D111" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E111" t="str">
-        <f>IF(ISNUMBER(MATCH(A111,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E111" t="s">
+        <v>13</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>10</v>
@@ -4604,9 +4557,8 @@
       <c r="D112" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E112" t="str">
-        <f>IF(ISNUMBER(MATCH(A112,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E112" t="s">
+        <v>10</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>10</v>
@@ -4625,9 +4577,8 @@
       <c r="D113" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E113" t="str">
-        <f>IF(ISNUMBER(MATCH(A113,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E113" t="s">
+        <v>13</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>10</v>
@@ -4646,9 +4597,8 @@
       <c r="D114" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E114" t="str">
-        <f>IF(ISNUMBER(MATCH(A114,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E114" t="s">
+        <v>10</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>10</v>
@@ -4667,9 +4617,8 @@
       <c r="D115" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E115" t="str">
-        <f>IF(ISNUMBER(MATCH(A115,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E115" t="s">
+        <v>13</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>10</v>
@@ -4688,9 +4637,8 @@
       <c r="D116" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E116" t="str">
-        <f>IF(ISNUMBER(MATCH(A116,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E116" t="s">
+        <v>13</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>10</v>
@@ -4709,9 +4657,8 @@
       <c r="D117" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E117" t="str">
-        <f>IF(ISNUMBER(MATCH(A117,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E117" t="s">
+        <v>13</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>10</v>
@@ -4730,9 +4677,8 @@
       <c r="D118" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E118" t="str">
-        <f>IF(ISNUMBER(MATCH(A118,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E118" t="s">
+        <v>10</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>10</v>
@@ -4751,9 +4697,8 @@
       <c r="D119" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E119" t="str">
-        <f>IF(ISNUMBER(MATCH(A119,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E119" t="s">
+        <v>13</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>10</v>
@@ -4772,9 +4717,8 @@
       <c r="D120" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E120" t="str">
-        <f>IF(ISNUMBER(MATCH(A120,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E120" t="s">
+        <v>10</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>10</v>
@@ -4793,9 +4737,8 @@
       <c r="D121" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E121" t="str">
-        <f>IF(ISNUMBER(MATCH(A121,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E121" t="s">
+        <v>10</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>10</v>
@@ -4814,9 +4757,8 @@
       <c r="D122" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E122" t="str">
-        <f>IF(ISNUMBER(MATCH(A122,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E122" t="s">
+        <v>10</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>10</v>
@@ -4835,9 +4777,8 @@
       <c r="D123" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E123" t="str">
-        <f>IF(ISNUMBER(MATCH(A123,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E123" t="s">
+        <v>13</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>10</v>
@@ -4857,7 +4798,7 @@
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>10</v>
@@ -4877,7 +4818,7 @@
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>10</v>
@@ -4896,9 +4837,8 @@
       <c r="D126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E126" t="str">
-        <f>IF(ISNUMBER(MATCH(A126,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E126" t="s">
+        <v>10</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>10</v>
@@ -4917,9 +4857,8 @@
       <c r="D127" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E127" t="str">
-        <f>IF(ISNUMBER(MATCH(A127,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E127" t="s">
+        <v>10</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>10</v>
@@ -4938,9 +4877,8 @@
       <c r="D128" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E128" t="str">
-        <f>IF(ISNUMBER(MATCH(A128,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E128" t="s">
+        <v>10</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>10</v>
@@ -4960,7 +4898,7 @@
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>10</v>
@@ -4980,7 +4918,7 @@
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F130" s="4" t="s">
         <v>10</v>
@@ -5000,7 +4938,7 @@
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F131" s="4" t="s">
         <v>10</v>
@@ -5019,9 +4957,8 @@
       <c r="D132" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E132" t="str">
-        <f>IF(ISNUMBER(MATCH(A132,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E132" t="s">
+        <v>13</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>10</v>
@@ -5040,9 +4977,8 @@
       <c r="D133" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E133" t="str">
-        <f>IF(ISNUMBER(MATCH(A133,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E133" t="s">
+        <v>13</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>10</v>
@@ -5061,9 +4997,8 @@
       <c r="D134" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E134" t="str">
-        <f>IF(ISNUMBER(MATCH(A134,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E134" t="s">
+        <v>13</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>10</v>
@@ -5082,9 +5017,8 @@
       <c r="D135" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E135" t="str">
-        <f>IF(ISNUMBER(MATCH(A135,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E135" t="s">
+        <v>13</v>
       </c>
       <c r="F135" s="4" t="s">
         <v>10</v>
@@ -5103,9 +5037,8 @@
       <c r="D136" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E136" t="str">
-        <f>IF(ISNUMBER(MATCH(A136,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E136" t="s">
+        <v>13</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>10</v>
@@ -5124,9 +5057,8 @@
       <c r="D137" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E137" t="str">
-        <f>IF(ISNUMBER(MATCH(A137,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E137" t="s">
+        <v>13</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>10</v>
@@ -5145,9 +5077,8 @@
       <c r="D138" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E138" t="str">
-        <f>IF(ISNUMBER(MATCH(A138,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E138" t="s">
+        <v>13</v>
       </c>
       <c r="F138" s="4" t="s">
         <v>10</v>
@@ -5166,9 +5097,8 @@
       <c r="D139" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E139" t="str">
-        <f>IF(ISNUMBER(MATCH(A139,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E139" t="s">
+        <v>13</v>
       </c>
       <c r="F139" s="4" t="s">
         <v>10</v>
@@ -5188,7 +5118,7 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>10</v>
@@ -5207,9 +5137,8 @@
       <c r="D141" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E141" t="str">
-        <f>IF(ISNUMBER(MATCH(A141,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E141" t="s">
+        <v>13</v>
       </c>
       <c r="F141" s="4" t="s">
         <v>10</v>
@@ -5228,9 +5157,8 @@
       <c r="D142" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E142" t="str">
-        <f>IF(ISNUMBER(MATCH(A142,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E142" t="s">
+        <v>13</v>
       </c>
       <c r="F142" s="4" t="s">
         <v>10</v>
@@ -5249,9 +5177,8 @@
       <c r="D143" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E143" t="str">
-        <f>IF(ISNUMBER(MATCH(A143,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E143" t="s">
+        <v>13</v>
       </c>
       <c r="F143" s="4" t="s">
         <v>10</v>
@@ -5270,9 +5197,8 @@
       <c r="D144" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E144" t="str">
-        <f>IF(ISNUMBER(MATCH(A144,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E144" t="s">
+        <v>13</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>10</v>
@@ -5291,9 +5217,8 @@
       <c r="D145" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E145" t="str">
-        <f>IF(ISNUMBER(MATCH(A145,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E145" t="s">
+        <v>13</v>
       </c>
       <c r="F145" s="4" t="s">
         <v>10</v>
@@ -5312,9 +5237,8 @@
       <c r="D146" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E146" t="str">
-        <f>IF(ISNUMBER(MATCH(A146,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E146" t="s">
+        <v>13</v>
       </c>
       <c r="F146" s="4" t="s">
         <v>10</v>
@@ -5333,9 +5257,8 @@
       <c r="D147" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E147" t="str">
-        <f>IF(ISNUMBER(MATCH(A147,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E147" t="s">
+        <v>13</v>
       </c>
       <c r="F147" s="4" t="s">
         <v>10</v>
@@ -5354,9 +5277,8 @@
       <c r="D148" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E148" t="str">
-        <f>IF(ISNUMBER(MATCH(A148,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E148" t="s">
+        <v>13</v>
       </c>
       <c r="F148" s="4" t="s">
         <v>10</v>
@@ -5375,9 +5297,8 @@
       <c r="D149" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E149" t="str">
-        <f>IF(ISNUMBER(MATCH(A149,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E149" t="s">
+        <v>13</v>
       </c>
       <c r="F149" s="4" t="s">
         <v>10</v>
@@ -5396,9 +5317,8 @@
       <c r="D150" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E150" t="str">
-        <f>IF(ISNUMBER(MATCH(A150,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E150" t="s">
+        <v>13</v>
       </c>
       <c r="F150" s="4" t="s">
         <v>10</v>
@@ -5417,9 +5337,8 @@
       <c r="D151" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E151" t="str">
-        <f>IF(ISNUMBER(MATCH(A151,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E151" t="s">
+        <v>13</v>
       </c>
       <c r="F151" s="4" t="s">
         <v>10</v>
@@ -5438,15 +5357,14 @@
       <c r="D152" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E152" t="str">
-        <f>IF(ISNUMBER(MATCH(A152,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E152" t="s">
+        <v>13</v>
       </c>
       <c r="F152" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" customFormat="1" spans="1:6">
       <c r="A153" t="s">
         <v>310</v>
       </c>
@@ -5459,15 +5377,14 @@
       <c r="D153" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E153" t="str">
-        <f>IF(ISNUMBER(MATCH(A153,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="E153" t="s">
+        <v>13</v>
       </c>
       <c r="F153" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" customFormat="1" spans="1:6">
       <c r="A154" t="s">
         <v>311</v>
       </c>
@@ -5480,15 +5397,14 @@
       <c r="D154" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E154" t="str">
-        <f>IF(ISNUMBER(MATCH(A154,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E154" t="s">
+        <v>13</v>
       </c>
       <c r="F154" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" customFormat="1" spans="1:6">
       <c r="A155" t="s">
         <v>312</v>
       </c>
@@ -5501,15 +5417,14 @@
       <c r="D155" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E155" t="str">
-        <f>IF(ISNUMBER(MATCH(A155,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E155" t="s">
+        <v>13</v>
       </c>
       <c r="F155" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" customFormat="1" spans="1:6">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -5522,15 +5437,14 @@
       <c r="D156" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E156" t="str">
-        <f>IF(ISNUMBER(MATCH(A156,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E156" t="s">
+        <v>13</v>
       </c>
       <c r="F156" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" customFormat="1" spans="1:6">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -5543,15 +5457,14 @@
       <c r="D157" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E157" t="str">
-        <f>IF(ISNUMBER(MATCH(A157,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E157" t="s">
+        <v>13</v>
       </c>
       <c r="F157" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" customFormat="1" spans="1:6">
       <c r="A158" t="s">
         <v>315</v>
       </c>
@@ -5564,15 +5477,14 @@
       <c r="D158" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E158" t="str">
-        <f>IF(ISNUMBER(MATCH(A158,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E158" t="s">
+        <v>13</v>
       </c>
       <c r="F158" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" customFormat="1" spans="1:6">
       <c r="A159" t="s">
         <v>316</v>
       </c>
@@ -5585,15 +5497,14 @@
       <c r="D159" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E159" t="str">
-        <f>IF(ISNUMBER(MATCH(A159,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E159" t="s">
+        <v>13</v>
       </c>
       <c r="F159" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" customFormat="1" spans="1:6">
       <c r="A160" t="s">
         <v>317</v>
       </c>
@@ -5606,15 +5517,14 @@
       <c r="D160" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E160" t="str">
-        <f>IF(ISNUMBER(MATCH(A160,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E160" t="s">
+        <v>13</v>
       </c>
       <c r="F160" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" customFormat="1" spans="1:6">
       <c r="A161" t="s">
         <v>318</v>
       </c>
@@ -5627,15 +5537,14 @@
       <c r="D161" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E161" t="str">
-        <f>IF(ISNUMBER(MATCH(A161,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E161" t="s">
+        <v>13</v>
       </c>
       <c r="F161" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" customFormat="1" spans="1:6">
       <c r="A162" t="s">
         <v>319</v>
       </c>
@@ -5648,15 +5557,14 @@
       <c r="D162" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E162" t="str">
-        <f>IF(ISNUMBER(MATCH(A162,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E162" t="s">
+        <v>13</v>
       </c>
       <c r="F162" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" customFormat="1" spans="1:6">
       <c r="A163" t="s">
         <v>320</v>
       </c>
@@ -5669,15 +5577,14 @@
       <c r="D163" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E163" t="str">
-        <f>IF(ISNUMBER(MATCH(A163,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E163" t="s">
+        <v>13</v>
       </c>
       <c r="F163" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" customFormat="1" spans="1:6">
       <c r="A164" t="s">
         <v>321</v>
       </c>
@@ -5690,15 +5597,14 @@
       <c r="D164" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E164" t="str">
-        <f>IF(ISNUMBER(MATCH(A164,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E164" t="s">
+        <v>13</v>
       </c>
       <c r="F164" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" customFormat="1" spans="1:6">
       <c r="A165" t="s">
         <v>322</v>
       </c>
@@ -5711,15 +5617,14 @@
       <c r="D165" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E165" t="str">
-        <f>IF(ISNUMBER(MATCH(A165,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E165" t="s">
+        <v>13</v>
       </c>
       <c r="F165" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" customFormat="1" spans="1:6">
       <c r="A166" t="s">
         <v>323</v>
       </c>
@@ -5733,13 +5638,13 @@
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F166" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" customFormat="1" spans="1:6">
       <c r="A167" t="s">
         <v>325</v>
       </c>
@@ -5752,15 +5657,14 @@
       <c r="D167" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E167" t="str">
-        <f>IF(ISNUMBER(MATCH(A167,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E167" t="s">
+        <v>13</v>
       </c>
       <c r="F167" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" customFormat="1" spans="1:6">
       <c r="A168" t="s">
         <v>327</v>
       </c>
@@ -5773,15 +5677,14 @@
       <c r="D168" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E168" t="str">
-        <f>IF(ISNUMBER(MATCH(A168,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E168" t="s">
+        <v>13</v>
       </c>
       <c r="F168" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" customFormat="1" spans="1:6">
       <c r="A169" t="s">
         <v>329</v>
       </c>
@@ -5794,15 +5697,14 @@
       <c r="D169" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E169" t="str">
-        <f>IF(ISNUMBER(MATCH(A169,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="E169" t="s">
+        <v>13</v>
       </c>
       <c r="F169" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1" spans="1:6">
+    <row r="170" customFormat="1" ht="15" customHeight="1" spans="1:6">
       <c r="A170" s="7" t="s">
         <v>331</v>
       </c>
@@ -5816,13 +5718,13 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F170" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" customFormat="1" spans="1:6">
       <c r="A171" t="s">
         <v>333</v>
       </c>
@@ -5836,13 +5738,13 @@
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F171" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" customFormat="1" spans="1:6">
       <c r="A172" t="s">
         <v>335</v>
       </c>
@@ -5856,13 +5758,13 @@
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F172" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" customFormat="1" spans="1:6">
       <c r="A173" t="s">
         <v>168</v>
       </c>
@@ -5876,13 +5778,13 @@
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F173" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" customFormat="1" spans="1:6">
       <c r="A174" t="s">
         <v>338</v>
       </c>
@@ -5896,13 +5798,13 @@
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F174" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" customFormat="1" spans="1:6">
       <c r="A175" t="s">
         <v>340</v>
       </c>
@@ -5916,13 +5818,13 @@
         <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F175" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" customFormat="1" spans="1:6">
       <c r="A176" t="s">
         <v>310</v>
       </c>
@@ -5936,13 +5838,13 @@
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F176" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" customFormat="1" spans="1:6">
       <c r="A177" t="s">
         <v>343</v>
       </c>
@@ -5956,13 +5858,13 @@
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F177" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" customFormat="1" spans="1:6">
       <c r="A178" t="s">
         <v>345</v>
       </c>
@@ -5976,13 +5878,13 @@
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F178" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" customFormat="1" spans="1:6">
       <c r="A179" t="s">
         <v>347</v>
       </c>
@@ -5996,13 +5898,13 @@
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F179" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" customFormat="1" spans="1:6">
       <c r="A180" t="s">
         <v>349</v>
       </c>
@@ -6016,7 +5918,7 @@
         <v>9</v>
       </c>
       <c r="E180" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F180" s="4" t="s">
         <v>10</v>
@@ -6036,7 +5938,7 @@
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F181" s="4" t="s">
         <v>10</v>
@@ -6056,14 +5958,214 @@
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="F182" s="4" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="183" customFormat="1" spans="1:6">
+      <c r="A183" t="s">
+        <v>355</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" customFormat="1" spans="1:6">
+      <c r="A184" t="s">
+        <v>357</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" customFormat="1" spans="1:6">
+      <c r="A185" t="s">
+        <v>359</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" customFormat="1" spans="1:6">
+      <c r="A186" t="s">
+        <v>361</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:6">
+      <c r="A187" t="s">
+        <v>363</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" spans="1:6">
+      <c r="A188" t="s">
+        <v>365</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:6">
+      <c r="A189" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" customFormat="1" spans="1:6">
+      <c r="A190" t="s">
+        <v>58</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" customFormat="1" spans="1:6">
+      <c r="A191" t="s">
+        <v>370</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" customFormat="1" spans="1:6">
+      <c r="A192" t="s">
+        <v>372</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F181" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F182" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B138">
@@ -6118,7 +6220,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -6148,7 +6250,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -6158,12 +6260,12 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -6173,7 +6275,7 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -6248,7 +6350,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:1">
@@ -6263,7 +6365,7 @@
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:1">
@@ -6298,7 +6400,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -6358,7 +6460,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -6378,7 +6480,7 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:1">
@@ -6393,7 +6495,7 @@
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -6429,12 +6531,12 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" ht="15.15" hidden="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A2)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6452,7 +6554,7 @@
     </row>
     <row r="4" ht="15.15" hidden="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A4)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6461,7 +6563,7 @@
     </row>
     <row r="5" ht="15.15" hidden="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A5)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6542,7 +6644,7 @@
     </row>
     <row r="14" ht="29.55" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="B14" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A14)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6551,7 +6653,7 @@
     </row>
     <row r="15" ht="29.55" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B15" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A15)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6650,7 +6752,7 @@
     </row>
     <row r="26" ht="15.15" hidden="1" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A26)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6821,7 +6923,7 @@
     </row>
     <row r="45" ht="87.15" hidden="1" spans="1:2">
       <c r="A45" s="3" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B45" t="e">
         <f>IF(COUNTIF(Sheet1!$A:$A,A45)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6875,7 +6977,7 @@
     </row>
     <row r="51" ht="15.15" hidden="1" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B51" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A51)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6911,7 +7013,7 @@
     </row>
     <row r="55" ht="15.15" hidden="1" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A55)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6983,7 +7085,7 @@
     </row>
     <row r="63" ht="15.15" hidden="1" spans="1:2">
       <c r="A63" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B63" t="str">
         <f>IF(COUNTIF(Sheet1!$A:$A,A63)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
